--- a/data/trans_camb/P36B08_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,26</t>
+          <t>26,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,0</t>
+          <t>23,54</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25,54</t>
+          <t>25,43</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,96</t>
+          <t>1,25; 14,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 14,93</t>
+          <t>2,85; 14,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 30,87</t>
+          <t>21,79; 31,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 19,2</t>
+          <t>7,09; 19,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,0</t>
+          <t>1,17; 14,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 29,21</t>
+          <t>18,71; 28,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 14,2</t>
+          <t>5,89; 14,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,23</t>
+          <t>3,92; 13,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,21; 29,0</t>
+          <t>22,43; 28,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 20,49</t>
+          <t>1,71; 21,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 22,46</t>
+          <t>3,86; 22,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 47,24</t>
+          <t>29,35; 47,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 27,44</t>
+          <t>9,17; 27,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 19,68</t>
+          <t>1,42; 19,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,72; 41,89</t>
+          <t>23,73; 41,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 20,54</t>
+          <t>8,03; 21,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 19,22</t>
+          <t>5,25; 19,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,76; 42,35</t>
+          <t>30,11; 42,07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31,01</t>
+          <t>31,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29,47</t>
+          <t>29,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 17,81</t>
+          <t>3,66; 17,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 20,88</t>
+          <t>7,55; 21,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 36,96</t>
+          <t>26,03; 37,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 17,31</t>
+          <t>3,43; 16,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,2</t>
+          <t>2,88; 16,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,62; 33,29</t>
+          <t>23,33; 33,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,45</t>
+          <t>5,01; 14,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,22</t>
+          <t>8,07; 16,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,46; 33,07</t>
+          <t>26,29; 33,57</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 29,79</t>
+          <t>5,6; 29,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 34,82</t>
+          <t>11,19; 35,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,6; 62,84</t>
+          <t>37,9; 62,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 26,53</t>
+          <t>4,85; 25,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 24,57</t>
+          <t>4,07; 25,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 52,0</t>
+          <t>31,92; 52,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 24,08</t>
+          <t>7,36; 23,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,97; 26,93</t>
+          <t>11,88; 26,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,49; 52,64</t>
+          <t>37,77; 53,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34,46</t>
+          <t>32,82</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,55</t>
+          <t>25,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32,42</t>
+          <t>31,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 17,16</t>
+          <t>6,38; 17,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 13,8</t>
+          <t>1,98; 13,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,87; 39,75</t>
+          <t>27,47; 37,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 20,64</t>
+          <t>2,66; 20,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 19,6</t>
+          <t>0,38; 19,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,89; 33,94</t>
+          <t>18,15; 33,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 16,76</t>
+          <t>7,48; 16,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 13,18</t>
+          <t>3,23; 13,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,79; 37,45</t>
+          <t>27,3; 34,98</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 28,89</t>
+          <t>9,81; 29,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 23,59</t>
+          <t>2,81; 22,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,03; 67,8</t>
+          <t>41,56; 64,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,94; 32,33</t>
+          <t>3,81; 32,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 31,25</t>
+          <t>0,5; 31,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,79; 55,57</t>
+          <t>24,03; 53,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,45; 27,63</t>
+          <t>11,39; 27,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,77; 21,78</t>
+          <t>4,77; 21,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,8; 61,81</t>
+          <t>40,3; 57,05</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29,16</t>
+          <t>29,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,97</t>
+          <t>24,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27,89</t>
+          <t>27,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,33</t>
+          <t>2,11; 10,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 10,6</t>
+          <t>2,22; 9,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,08; 32,5</t>
+          <t>26,41; 32,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 12,42</t>
+          <t>2,6; 11,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 8,96</t>
+          <t>0,14; 9,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,31; 28,9</t>
+          <t>20,44; 27,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,79</t>
+          <t>3,64; 9,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,64</t>
+          <t>3,07; 8,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,74; 30,98</t>
+          <t>25,27; 29,89</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,86; 16,33</t>
+          <t>3,34; 16,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 17,06</t>
+          <t>3,27; 15,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,93; 52,53</t>
+          <t>39,44; 52,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 18,17</t>
+          <t>3,54; 17,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 13,02</t>
+          <t>0,16; 14,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,77; 42,54</t>
+          <t>27,65; 41,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,97</t>
+          <t>5,19; 14,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,22</t>
+          <t>4,5; 13,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37,37; 47,58</t>
+          <t>36,76; 45,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33,73</t>
+          <t>34,49</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,52</t>
+          <t>24,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>28,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 18,41</t>
+          <t>4,95; 18,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 20,47</t>
+          <t>7,17; 20,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27,85; 39,69</t>
+          <t>28,41; 40,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,81</t>
+          <t>2,82; 12,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 12,21</t>
+          <t>2,11; 12,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,53; 28,79</t>
+          <t>20,03; 28,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,36</t>
+          <t>5,26; 13,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,44</t>
+          <t>5,56; 13,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24,94; 31,9</t>
+          <t>24,76; 31,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,43; 33,54</t>
+          <t>7,93; 33,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,09; 37,86</t>
+          <t>11,44; 38,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43,77; 74,12</t>
+          <t>45,44; 76,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,9; 18,94</t>
+          <t>3,87; 19,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,78; 18,13</t>
+          <t>3,18; 18,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,31; 42,76</t>
+          <t>26,78; 41,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,38; 20,92</t>
+          <t>7,66; 20,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,64; 20,94</t>
+          <t>8,05; 21,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>36,04; 51,12</t>
+          <t>35,98; 50,13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37,01</t>
+          <t>37,82</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,28</t>
+          <t>23,86</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25,65</t>
+          <t>26,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 7,02</t>
+          <t>-10,8; 5,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,21; 18,64</t>
+          <t>2,06; 18,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26,14; 44,97</t>
+          <t>28,77; 45,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,08; 11,49</t>
+          <t>4,03; 10,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,9</t>
+          <t>0,47; 8,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,23; 26,53</t>
+          <t>20,9; 26,74</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,27</t>
+          <t>2,38; 9,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,8</t>
+          <t>1,92; 8,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>22,11; 28,61</t>
+          <t>23,45; 29,48</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 14,5</t>
+          <t>-19,23; 12,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,87; 39,3</t>
+          <t>3,64; 38,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48,01; 96,06</t>
+          <t>51,66; 96,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,58</t>
+          <t>5,53; 15,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,89; 11,35</t>
+          <t>0,63; 11,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,75; 38,52</t>
+          <t>28,5; 38,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,6; 14,13</t>
+          <t>3,43; 14,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2,99; 13,38</t>
+          <t>2,76; 13,47</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31,92; 43,72</t>
+          <t>33,81; 45,18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31,23</t>
+          <t>31,14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,84</t>
+          <t>24,68</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>27,99</t>
+          <t>27,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,58; 10,39</t>
+          <t>5,6; 10,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,47</t>
+          <t>6,75; 11,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29,3; 33,33</t>
+          <t>29,16; 33,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,6</t>
+          <t>6,37; 10,5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,4</t>
+          <t>4,2; 8,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,03; 26,52</t>
+          <t>23,08; 26,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,71; 9,71</t>
+          <t>6,65; 9,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,27</t>
+          <t>6,07; 9,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>26,61; 29,44</t>
+          <t>26,6; 29,08</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,77</t>
+          <t>8,68; 16,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,83; 18,55</t>
+          <t>10,46; 18,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45,35; 54,0</t>
+          <t>44,87; 53,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,93; 15,16</t>
+          <t>8,83; 15,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,96</t>
+          <t>5,82; 11,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,6; 38,02</t>
+          <t>31,76; 37,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,89; 14,62</t>
+          <t>9,7; 14,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,96; 13,89</t>
+          <t>8,94; 13,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38,99; 44,43</t>
+          <t>38,97; 44,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P36B08_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
